--- a/incomplete/reduction_10.1021.acssuschemeng.3c01544.xlsx
+++ b/incomplete/reduction_10.1021.acssuschemeng.3c01544.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/core/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/incomplete/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16A23F2-677A-CA44-9A3C-11D44873B1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF235382-C19D-E540-A96D-EDFEF0B0E2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="540" yWindow="500" windowWidth="23940" windowHeight="15360" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="60">
   <si>
     <t>REACTION</t>
   </si>
@@ -95,9 +95,6 @@
     <t>C1=CC(=CC=C1CBr)Br</t>
   </si>
   <si>
-    <t>TEMPTERATURE</t>
-  </si>
-  <si>
     <t>Temperature (Celsius)</t>
   </si>
   <si>
@@ -216,6 +213,9 @@
   </si>
   <si>
     <t>Thermocouple Internal</t>
+  </si>
+  <si>
+    <t>TEMPERATURE</t>
   </si>
 </sst>
 </file>
@@ -819,16 +819,16 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="E4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
         <v>55</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:21" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
@@ -837,16 +837,16 @@
         <v>16</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>57</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>58</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -887,11 +887,9 @@
       <c r="K7" s="1"/>
       <c r="L7" s="4"/>
       <c r="M7" t="s">
-        <v>19</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>6</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="T7" s="3"/>
       <c r="U7" s="4"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
@@ -924,7 +922,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>11</v>
@@ -933,14 +931,10 @@
         <v>3</v>
       </c>
       <c r="N8" t="s">
-        <v>20</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>8</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="T8" s="5"/>
+      <c r="U8" s="6"/>
     </row>
     <row r="9" spans="1:21" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
@@ -975,24 +969,24 @@
         <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" s="6">
         <v>0.05</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K10">
         <v>18</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N10">
         <v>45</v>
@@ -1013,24 +1007,24 @@
         <v>1</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G11" s="6">
         <v>0.05</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K11">
         <v>18</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N11">
         <v>120</v>
@@ -1051,24 +1045,24 @@
         <v>1</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" s="6">
         <v>0.05</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12">
         <v>18</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N12">
         <v>120</v>
@@ -1077,27 +1071,27 @@
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G13" s="6">
         <v>0.05</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I13" s="6">
         <v>72</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K13">
         <v>18</v>
@@ -1109,31 +1103,31 @@
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="6">
         <v>1</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" s="6">
         <v>2</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G14" s="6">
         <v>0.05</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I14" s="6">
         <v>52</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K14">
         <v>18</v>
@@ -1145,31 +1139,31 @@
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" s="6">
         <v>2</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" s="6">
         <v>0.05</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I15" s="6">
         <v>34</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K15">
         <v>18</v>
@@ -1181,29 +1175,29 @@
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G16" s="6">
         <v>0.05</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I16" s="6">
         <v>38</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K16">
         <v>18</v>
@@ -1212,7 +1206,7 @@
         <v>3600</v>
       </c>
       <c r="M16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N16">
         <v>90</v>
@@ -1221,31 +1215,31 @@
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
       <c r="B17" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="6">
         <v>0.5</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="6">
         <v>0.5</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G17" s="6">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I17" s="6">
         <v>48</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K17">
         <v>18</v>
@@ -1254,7 +1248,7 @@
         <v>3600</v>
       </c>
       <c r="M17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N17">
         <v>90</v>
@@ -1263,15 +1257,15 @@
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="18"/>
@@ -1279,7 +1273,7 @@
         <v>57</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K18">
         <v>18</v>
@@ -1291,15 +1285,15 @@
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
       <c r="B19" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="18"/>
@@ -1307,7 +1301,7 @@
         <v>63</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K19">
         <v>18</v>
@@ -1319,15 +1313,15 @@
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="15"/>
       <c r="B20" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="18"/>
@@ -1335,7 +1329,7 @@
         <v>60</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K20">
         <v>18</v>
@@ -1347,31 +1341,31 @@
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
       <c r="B21" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="6">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" s="6">
         <v>1</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G21" s="6">
         <v>0.05</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I21" s="6">
         <v>99</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K21">
         <v>18</v>
@@ -1383,15 +1377,15 @@
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="15"/>
       <c r="B22" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="18"/>
@@ -1399,7 +1393,7 @@
         <v>57</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K22">
         <v>18</v>
@@ -1411,31 +1405,31 @@
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
       <c r="B23" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" s="6">
         <v>1</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G23" s="6">
         <v>0.05</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I23" s="6">
         <v>46</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K23">
         <v>18</v>
@@ -1447,31 +1441,31 @@
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="15"/>
       <c r="B24" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="6">
         <v>0.5</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" s="6">
         <v>1.5</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G24" s="6">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I24" s="6">
         <v>54</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K24">
         <v>18</v>
@@ -1483,19 +1477,19 @@
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
       <c r="B25" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" s="6">
         <v>0.5</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" s="6">
         <v>1.5</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G25" s="6">
         <v>2.5000000000000001E-2</v>
@@ -1505,7 +1499,7 @@
         <v>54</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K25">
         <v>18</v>
@@ -1517,31 +1511,31 @@
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="15"/>
       <c r="B26" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="6">
         <v>1</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" s="6">
         <v>1</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G26" s="6">
         <v>0.5</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I26" s="6">
         <v>67</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K26">
         <v>18</v>
@@ -1553,15 +1547,15 @@
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
       <c r="B27" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="18"/>
@@ -1569,7 +1563,7 @@
         <v>74</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K27">
         <v>18</v>
@@ -1581,15 +1575,15 @@
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="15"/>
       <c r="B28" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="18"/>
@@ -1597,7 +1591,7 @@
         <v>99</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K28">
         <v>18</v>
@@ -1619,7 +1613,7 @@
         <v>99</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K29">
         <v>18</v>
